--- a/assignment_01_improved.xlsx
+++ b/assignment_01_improved.xlsx
@@ -544,7 +544,7 @@
         <v>106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003318</v>
+        <v>5.612999999999999e-05</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -626,7 +626,7 @@
         <v>99</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003304</v>
+        <v>5.549999999999999e-05</v>
       </c>
       <c r="J3" t="n">
         <v>66</v>
@@ -676,7 +676,7 @@
         <v>102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003304</v>
+        <v>5.568e-05</v>
       </c>
       <c r="J4" t="n">
         <v>73</v>
@@ -758,7 +758,7 @@
         <v>117</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003334</v>
+        <v>5.703e-05</v>
       </c>
       <c r="J5" t="n">
         <v>81</v>
@@ -840,7 +840,7 @@
         <v>91</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000326</v>
+        <v>5.435999999999999e-05</v>
       </c>
       <c r="J6" t="n">
         <v>63</v>
@@ -922,7 +922,7 @@
         <v>96</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000327</v>
+        <v>5.480999999999999e-05</v>
       </c>
       <c r="J7" t="n">
         <v>69</v>
@@ -972,7 +972,7 @@
         <v>119</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003356</v>
+        <v>5.747999999999999e-05</v>
       </c>
       <c r="J8" t="n">
         <v>73</v>
@@ -1022,7 +1022,7 @@
         <v>97</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0003300000000000001</v>
+        <v>5.531999999999999e-05</v>
       </c>
       <c r="J9" t="n">
         <v>69</v>
@@ -1104,7 +1104,7 @@
         <v>88</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000326</v>
+        <v>5.417999999999999e-05</v>
       </c>
       <c r="J10" t="n">
         <v>63</v>
@@ -1154,7 +1154,7 @@
         <v>103</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0003308</v>
+        <v>5.579999999999999e-05</v>
       </c>
       <c r="J11" t="n">
         <v>65</v>
@@ -1204,7 +1204,7 @@
         <v>112</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0003308</v>
+        <v>5.633999999999999e-05</v>
       </c>
       <c r="J12" t="n">
         <v>79</v>
@@ -1286,7 +1286,7 @@
         <v>121</v>
       </c>
       <c r="I13" t="n">
-        <v>0.000334</v>
+        <v>5.735999999999999e-05</v>
       </c>
       <c r="J13" t="n">
         <v>77</v>
@@ -1368,7 +1368,7 @@
         <v>112</v>
       </c>
       <c r="I14" t="n">
-        <v>0.000333</v>
+        <v>5.666999999999999e-05</v>
       </c>
       <c r="J14" t="n">
         <v>72</v>
@@ -1418,7 +1418,7 @@
         <v>89</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0003262</v>
+        <v>5.426999999999999e-05</v>
       </c>
       <c r="J15" t="n">
         <v>67</v>
@@ -1500,7 +1500,7 @@
         <v>104</v>
       </c>
       <c r="I16" t="n">
-        <v>0.000329</v>
+        <v>5.558999999999999e-05</v>
       </c>
       <c r="J16" t="n">
         <v>72</v>
@@ -1550,7 +1550,7 @@
         <v>102</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000331</v>
+        <v>5.576999999999999e-05</v>
       </c>
       <c r="J17" t="n">
         <v>68</v>
@@ -1632,7 +1632,7 @@
         <v>108</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0003332</v>
+        <v>5.646e-05</v>
       </c>
       <c r="J18" t="n">
         <v>64</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0003316</v>
+        <v>5.658e-05</v>
       </c>
       <c r="J19" t="n">
         <v>79</v>
@@ -1764,7 +1764,7 @@
         <v>97</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0003284</v>
+        <v>5.507999999999999e-05</v>
       </c>
       <c r="J20" t="n">
         <v>59</v>
@@ -1846,7 +1846,7 @@
         <v>119</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0003326</v>
+        <v>5.702999999999999e-05</v>
       </c>
       <c r="J21" t="n">
         <v>77</v>
@@ -1896,7 +1896,7 @@
         <v>75</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0003234000000000001</v>
+        <v>5.301e-05</v>
       </c>
       <c r="J22" t="n">
         <v>53</v>
@@ -1946,7 +1946,7 @@
         <v>93</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0003272</v>
+        <v>5.466e-05</v>
       </c>
       <c r="J23" t="n">
         <v>69</v>
@@ -1996,7 +1996,7 @@
         <v>98</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0003288</v>
+        <v>5.519999999999999e-05</v>
       </c>
       <c r="J24" t="n">
         <v>72</v>
@@ -2078,7 +2078,7 @@
         <v>83</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0003242</v>
+        <v>5.361e-05</v>
       </c>
       <c r="J25" t="n">
         <v>65</v>
@@ -2128,7 +2128,7 @@
         <v>90</v>
       </c>
       <c r="I26" t="n">
-        <v>0.000326</v>
+        <v>5.43e-05</v>
       </c>
       <c r="J26" t="n">
         <v>65</v>
@@ -2178,7 +2178,7 @@
         <v>81</v>
       </c>
       <c r="I27" t="n">
-        <v>0.000324</v>
+        <v>5.345999999999999e-05</v>
       </c>
       <c r="J27" t="n">
         <v>58</v>
@@ -2228,7 +2228,7 @@
         <v>104</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0003298</v>
+        <v>5.570999999999999e-05</v>
       </c>
       <c r="J28" t="n">
         <v>75</v>
@@ -2278,7 +2278,7 @@
         <v>84</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0003244</v>
+        <v>5.37e-05</v>
       </c>
       <c r="J29" t="n">
         <v>63</v>
@@ -2360,7 +2360,7 @@
         <v>75</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0003236</v>
+        <v>5.304e-05</v>
       </c>
       <c r="J30" t="n">
         <v>54</v>
@@ -2410,7 +2410,7 @@
         <v>97</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0003274</v>
+        <v>5.493e-05</v>
       </c>
       <c r="J31" t="n">
         <v>68</v>
@@ -2460,7 +2460,7 @@
         <v>98</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0003294</v>
+        <v>5.528999999999999e-05</v>
       </c>
       <c r="J32" t="n">
         <v>69</v>
@@ -2510,7 +2510,7 @@
         <v>91</v>
       </c>
       <c r="I33" t="n">
-        <v>0.000327</v>
+        <v>5.451e-05</v>
       </c>
       <c r="J33" t="n">
         <v>68</v>
@@ -2560,7 +2560,7 @@
         <v>99</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0003298</v>
+        <v>5.541e-05</v>
       </c>
       <c r="J34" t="n">
         <v>68</v>
@@ -2610,7 +2610,7 @@
         <v>106</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0003294</v>
+        <v>5.577e-05</v>
       </c>
       <c r="J35" t="n">
         <v>74</v>
@@ -2660,7 +2660,7 @@
         <v>110</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0003302</v>
+        <v>5.612999999999999e-05</v>
       </c>
       <c r="J36" t="n">
         <v>71</v>
@@ -2710,7 +2710,7 @@
         <v>108</v>
       </c>
       <c r="I37" t="n">
-        <v>0.000331</v>
+        <v>5.613e-05</v>
       </c>
       <c r="J37" t="n">
         <v>76</v>
@@ -2760,7 +2760,7 @@
         <v>93</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0003274</v>
+        <v>5.468999999999999e-05</v>
       </c>
       <c r="J38" t="n">
         <v>68</v>
@@ -2810,7 +2810,7 @@
         <v>93</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0003306</v>
+        <v>5.517e-05</v>
       </c>
       <c r="J39" t="n">
         <v>53</v>
@@ -2860,7 +2860,7 @@
         <v>94</v>
       </c>
       <c r="I40" t="n">
-        <v>0.000327</v>
+        <v>5.468999999999999e-05</v>
       </c>
       <c r="J40" t="n">
         <v>67</v>
@@ -2910,7 +2910,7 @@
         <v>87</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0003256000000000001</v>
+        <v>5.405999999999999e-05</v>
       </c>
       <c r="J41" t="n">
         <v>52</v>
@@ -2960,7 +2960,7 @@
         <v>90</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0003266</v>
+        <v>5.439e-05</v>
       </c>
       <c r="J42" t="n">
         <v>60</v>
@@ -3010,7 +3010,7 @@
         <v>93</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0003268</v>
+        <v>5.46e-05</v>
       </c>
       <c r="J43" t="n">
         <v>66</v>
@@ -3060,7 +3060,7 @@
         <v>98</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0003284</v>
+        <v>5.514e-05</v>
       </c>
       <c r="J44" t="n">
         <v>64</v>
@@ -3110,7 +3110,7 @@
         <v>108</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0003336</v>
+        <v>5.652e-05</v>
       </c>
       <c r="J45" t="n">
         <v>65</v>
@@ -3192,7 +3192,7 @@
         <v>124</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0003356</v>
+        <v>5.778e-05</v>
       </c>
       <c r="J46" t="n">
         <v>82</v>
@@ -3242,7 +3242,7 @@
         <v>106</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0003312</v>
+        <v>5.604e-05</v>
       </c>
       <c r="J47" t="n">
         <v>71</v>
@@ -3292,7 +3292,7 @@
         <v>104</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0003312</v>
+        <v>5.591999999999999e-05</v>
       </c>
       <c r="J48" t="n">
         <v>65</v>
@@ -3342,7 +3342,7 @@
         <v>105</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0003334</v>
+        <v>5.630999999999999e-05</v>
       </c>
       <c r="J49" t="n">
         <v>57</v>
@@ -3392,7 +3392,7 @@
         <v>118</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0003338</v>
+        <v>5.714999999999999e-05</v>
       </c>
       <c r="J50" t="n">
         <v>79</v>
@@ -3442,7 +3442,7 @@
         <v>119</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0003352</v>
+        <v>5.742e-05</v>
       </c>
       <c r="J51" t="n">
         <v>70</v>
